--- a/Exam/gymtrackerpro/lib/controller/__tests__/bbt/workout-session-controller/getWorkoutSession-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/bbt/workout-session-controller/getWorkoutSession-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="63">
-  <si>
-    <t>Statement: workout-session-controller.getWorkoutSession(workoutSessionId) – Server Action. No input validation. Delegates to workoutSessionService.getWorkoutSession(). Returns ActionResult&lt;WorkoutSessionWithExercises&gt;.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="67">
+  <si>
+    <t>Statement: getWorkoutSession(id) – Looks up a workout session by the provided id and returns an ActionResult&lt;WorkoutSessionWithExercises&gt;. Returns success with the matching session on success. Returns a failure with the service error message for NotFoundError. Returns a failure with message "An unexpected error occurred" for any other unexpected error.</t>
   </si>
   <si>
     <t/>
@@ -31,27 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: workoutSessionId: string</t>
+    <t>Input: id: string</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>workoutSessionService.getWorkoutSession is mock-injected</t>
+    <t>A known session id exists in the store. A non-existent id has no matching record.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: ActionResult&lt;WorkoutSessionWithExercises&gt;</t>
+    <t>Output: Promise&lt;ActionResult&lt;WorkoutSessionWithExercises&gt;&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t xml:space="preserve">On success: WorkoutSessionWithExercises returned.
-On NotFoundError: failure.
-On error: generic failure.</t>
+    <t>On success: session retrieved successfully, returned data matches the stored session. On NotFoundError: operation fails with the service error message. On unexpected error: operation fails with message "An unexpected error occurred".</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -66,16 +64,19 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>session existence</t>
-  </si>
-  <si>
-    <t>service resolves WorkoutSessionWithExercises</t>
-  </si>
-  <si>
-    <t>service throws NotFoundError → failure</t>
-  </si>
-  <si>
-    <t>service throws Error → generic failure</t>
+    <t>ID existence</t>
+  </si>
+  <si>
+    <t>Known existing id → session retrieved successfully, returned data matches the stored session</t>
+  </si>
+  <si>
+    <t>Non-existent id (NotFoundError "Session not found") → operation fails with message "Session not found"</t>
+  </si>
+  <si>
+    <t>Error type</t>
+  </si>
+  <si>
+    <t>Unexpected error occurs → operation fails with message "An unexpected error occurred"</t>
   </si>
   <si>
     <t>No TC</t>
@@ -93,31 +94,34 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>id="session-001", service resolves</t>
-  </si>
-  <si>
-    <t>{ success: true, data: WorkoutSessionWithExercises }</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>"nonexistent-id", service throws NotFoundError</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "Workout session not found" }</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>id="session-001", service throws Error</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "An unexpected error occurred" }</t>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>known existing session id, session is retrieved successfully</t>
+  </si>
+  <si>
+    <t>session retrieved successfully, returned data matches the stored session</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>non-existent id, no matching record exists (NotFoundError "Session not found")</t>
+  </si>
+  <si>
+    <t>operation fails with message "Session not found"</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>known existing session id, an unexpected error occurs during retrieval</t>
+  </si>
+  <si>
+    <t>operation fails with message "An unexpected error occurred"</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -126,46 +130,55 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>ID is opaque string</t>
+    <t>ID length</t>
+  </si>
+  <si>
+    <t>id: "" (length 0): no record can match → operation fails with message "Session not found"</t>
+  </si>
+  <si>
+    <t>id: "a" (length 1), no matching record exists → operation fails with message "Session not found"</t>
+  </si>
+  <si>
+    <t>id: "a" (length 1), a matching session record exists → session retrieved successfully, returned data id is "a"</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
+    <t>BVA-1 (len=0)</t>
+  </si>
+  <si>
+    <t>id: "" (empty string), no matching record exists (NotFoundError "Session not found")</t>
+  </si>
+  <si>
+    <t>BVA-2 (len=1, miss)</t>
+  </si>
+  <si>
+    <t>id: "a" (1 character), no matching record exists (NotFoundError "Session not found")</t>
+  </si>
+  <si>
+    <t>BVA-3 (len=1, hit)</t>
+  </si>
+  <si>
+    <t>id: "a" (1 character), a matching session record exists with id "a", session is retrieved successfully</t>
+  </si>
+  <si>
+    <t>session retrieved successfully, returned data id is "a"</t>
+  </si>
+  <si>
     <t>TC from EC</t>
   </si>
   <si>
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
-    <t>Existing session id</t>
-  </si>
-  <si>
-    <t>success=true, session returned</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>Non-existent id</t>
-  </si>
-  <si>
-    <t>success=false, message from NotFoundError</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>Service throws unexpected Error</t>
-  </si>
-  <si>
-    <t>success=false, message="An unexpected error occurred"</t>
+    <t>BVA-1</t>
+  </si>
+  <si>
+    <t>BVA-2</t>
+  </si>
+  <si>
+    <t>BVA-3</t>
   </si>
   <si>
     <t>Testing</t>
@@ -198,16 +211,13 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>WSM-05</t>
+    <t>CTRL-23</t>
   </si>
   <si>
     <t>n/a</t>
   </si>
   <si>
     <t>not yet</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -764,7 +774,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
@@ -778,13 +788,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -807,19 +817,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -827,16 +837,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -844,16 +854,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -861,16 +871,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -881,7 +891,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -891,13 +901,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -905,10 +915,32 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -919,7 +951,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -931,19 +963,70 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -954,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -967,22 +1050,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -990,19 +1073,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1010,19 +1093,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1030,19 +1113,79 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>48</v>
+      <c r="F7" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1070,16 +1213,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1087,45 +1230,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="I2" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>59</v>
+      <c r="A3" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="B3" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1134,19 +1277,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>62</v>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
